--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Norstella</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, PyTorch, S3</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37294b654b8dfdfa</t>
+          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer, Machine Learning AI</t>
+          <t>Senior PS Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mSupply</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, AWS SageMaker</t>
+          <t>PyTorch, XGBoost, Azure ML, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=312b829ea695631a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Data Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>AssetWorks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, S3, Glue, Data Lake, MLflow</t>
+          <t>S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d863f11ee6e4e4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Consultant, Data Science &amp; Analytics</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TransUnion</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, Glue, Redshift, Redshift, PySpark, PostgreSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ec03fca9cb552c1</t>
+          <t>https://www.indeed.com/viewjob?jk=81f5740eb2b80cdd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EBSCO Information Services</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, S3, Glue, Data Lake, MLflow, Docker, CI/CD, Jenkins</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7cfaf26e34fa908</t>
+          <t>https://www.indeed.com/viewjob?jk=d1a416f1f2e6d0cf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI/Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mission Produce</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Oxnard, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Synapse, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,277 +671,277 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adb3f80bc7a0023f</t>
+          <t>https://www.indeed.com/viewjob?jk=e147109fd8e76890</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud Engineer-Analyst-Dallas</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Glue, Data Lake, Docker, Apache Airflow, CI/CD, Terraform, Snowflake, Kafka</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cd695a259528ee8</t>
+          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior ML Engineer II</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, TensorFlow, PyTorch, MLflow, CI/CD, Kafka</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f1aa8551c5f292</t>
+          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Gen AI Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Keras, FastAPI, AKS</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=daa38ce41d64114b</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Prompt Engineering, Docker, Kubernetes, Jenkins, Terraform, Git, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4b1c757ee83233</t>
+          <t>https://www.indeed.com/viewjob?jk=a48046ca1048d763</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nexus Health Systems</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, FastAPI, Terraform</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a97046d9a2119c</t>
+          <t>https://www.indeed.com/viewjob?jk=63850baa7eee8069</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Enterprise Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wolters Kluwer</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Riverwoods, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bc224de87d1e85f</t>
+          <t>https://www.indeed.com/viewjob?jk=98d4387c2654c589</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Asset &amp; Wealth Management-Cloud SRE Engineer-Associate-Dallas</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fa6ef3e26d36408</t>
+          <t>https://www.indeed.com/viewjob?jk=3c0f06b76a2f879e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Kinesis, MLflow, Git, Databricks, Redshift</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e29cc99694e4c30d</t>
+          <t>https://www.indeed.com/viewjob?jk=a27146f1cf93e2d5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior ML Engineer I</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, LLaMA, Mistral, Hugging Face, Pinecone, TensorFlow, PyTorch, CI/CD</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,172 +986,172 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406037212a73ee07</t>
+          <t>https://www.indeed.com/viewjob?jk=a436fa38d8dc9248</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Innovation Consultant (Agentic AI Consulting)</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>CHAPSVISION</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, Copilot, MLflow, FastAPI, Git, Snowflake, Databricks</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6fe183c46de7cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=d9570e50091d93b6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Applied AI &amp; ML Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bose</t>
+          <t>Follett Corporation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Framingham, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, MLflow, Git, Snowflake, Databricks, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c65fe5cea490224</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf551020314ef23</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Infrastructure Software Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cornerstone OnDemand</t>
+          <t>Jack Henry &amp; Associates</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Kafka, MongoDB, Cassandra, NoSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62cf7aec7b000416</t>
+          <t>https://www.indeed.com/viewjob?jk=310ddc8ba4edc4a9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Just Appraised</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Leesburg, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30341d57d648c0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7ffcf669df64a8de</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Implementation</t>
+          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Just Appraised</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Data Lake, Kinesis, Snowflake, PySpark, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd84983d5cd59ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>Full-stack Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Manulife</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=928bf373200d5d63</t>
+          <t>https://www.indeed.com/viewjob?jk=6d34396f850f076e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HPC Infrastructure DevOps Engineer II</t>
+          <t>Data Scientist 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>St. Jude Children's Research Hospital</t>
+          <t>TSP LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, CI/CD, Terraform, Git, Python, R</t>
+          <t>Data Scientist, Git, Snowflake, Databricks, PySpark, Tableau, Quicksight, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33d99912f848c6f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8136792201f6bfb8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Entrata</t>
+          <t>PropertyPilot</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Manasquan, NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Apache Airflow, Git, Python, R, Java</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,777 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc55972fd32a164</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Software Engineer - AI</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Just Appraised</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4425d2727338f1b6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Machine Learning (ML)</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Norstella</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, S3, Git, Snowflake, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84fc493dabc21c6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=acbe895c0ce55c03</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf32c2f108f12740</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=edc3e71972f0b261</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c81e36c10866607d</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Senior Distinguished Engineer, AI Compute (Remote Eligible)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Information Technology Senior Management Forum</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, EC2, Kubernetes, Dask, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf8f16b7446dcdaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MTS III, Software</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Panasonic</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Irvine, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=638e1245e51a0998</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI Engineering Intern - Summer 2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Lenovo</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fc87402dd2610d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Software Engineer - QuantumBlack, AI by McKinsey</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>McKinsey &amp; Company</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Jenkins, Git, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3af348066fe5800e</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Network Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bad4863775b62604</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Metrics Engineer - Grafana</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Generative AI, Jenkins, Terraform, Git, NoSQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f968d07ba6cb70f4</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Sr. AI Architect</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Cyclotron</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Copilot, Mistral, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61aee83a5c4f987b</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FreshDirect</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Woodbridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, CI/CD, MySQL, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dd89ce8b7ba4018</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Python Developer / Engineer (US)</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>TD</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Mount Laurel, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Git, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=572eaf4aa7ac3381</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Sr. Analyst, Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Restaurant Brands International</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93cf59a5795f34b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=37b16c0a520ed870</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Software Engineer - Full Stack (Angular, Java)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Equifax</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CI/CD, Jenkins, Terraform, Git, MySQL, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=379982f5d50d52bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ML Engineer II</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a6457f20d674b3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Forward Deployed Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Arcade Food Theatre</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>LangChain, LLaMA, Kubernetes, CI/CD, Databricks, MongoDB, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbab54f5ea5c9baa</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>SLB</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=437c626ef3cfc90d</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test (SDET)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Tradeweb</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d60808e649d31ec2</t>
+          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer - Insurance Domain - HYBRID</t>
+          <t>Software Engineer III - Python AI/ML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Warren, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering</t>
+          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31b5a55badae894d</t>
+          <t>https://www.indeed.com/viewjob?jk=c05b83413ef699f8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Software Engineer III - Python/AWS/Kafka</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,77 +521,77 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PyTorch, XGBoost, Azure ML, Redshift, BigQuery, Synapse, Snowflake, Databricks, BigQuery, Redshift</t>
+          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfc1ac7dc950d681</t>
+          <t>https://www.indeed.com/viewjob?jk=0b1af3e74c0a5456</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Enterprise AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AssetWorks</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Azure ML, Synapse, CI/CD, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6de4a61bfe7bafa4</t>
+          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist, Marketing Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81f5740eb2b80cdd</t>
+          <t>https://www.indeed.com/viewjob?jk=710a55c7263d5b09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer I, AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, PyTorch, OpenCV, S3, EC2, Docker, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a416f1f2e6d0cf</t>
+          <t>https://www.indeed.com/viewjob?jk=868c1db97a70677e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Engineer I, AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, PyTorch, OpenCV, S3, EC2, Docker, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e147109fd8e76890</t>
+          <t>https://www.indeed.com/viewjob?jk=d12156e8fb489dcf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Willingboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, RAG, Redshift, Data Lake, CI/CD, Git, Snowflake, Databricks, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efd50ec9fe32e19</t>
+          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+          <t>LangChain, RAG, FAISS, S3, Redshift, Data Lake, CI/CD, GitHub Actions, Git, Redshift</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea58757f9149ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineering Intern</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Bright Machines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd2db53316f326e</t>
+          <t>https://www.indeed.com/viewjob?jk=961161799c7db2e3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>Nexnovels</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,104 +801,104 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a48046ca1048d763</t>
+          <t>https://www.indeed.com/viewjob?jk=75efa56b5158387e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63850baa7eee8069</t>
+          <t>https://www.indeed.com/viewjob?jk=245c39b07398f5a8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d4387c2654c589</t>
+          <t>https://www.indeed.com/viewjob?jk=1389dbc20ceca1f2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Clemente, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0f06b76a2f879e</t>
+          <t>https://www.indeed.com/viewjob?jk=8b5d6530b9c6e9c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Escondido, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a27146f1cf93e2d5</t>
+          <t>https://www.indeed.com/viewjob?jk=91b5cd590389fcb8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Kubernetes, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,234 +986,234 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a436fa38d8dc9248</t>
+          <t>https://www.indeed.com/viewjob?jk=23a60a85ba8e33b8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHAPSVISION</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9570e50091d93b6</t>
+          <t>https://www.indeed.com/viewjob?jk=04eed1b8662a64c3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Follett Corporation</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Sparks, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf551020314ef23</t>
+          <t>https://www.indeed.com/viewjob?jk=639c879094c2c1d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Infrastructure Software Engineer I</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jack Henry &amp; Associates</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Oceanside, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Dataflow, Docker, Kubernetes, Terraform, Git, BigQuery, MongoDB, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=310ddc8ba4edc4a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a2de883e7fa22dc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Commence</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Leesburg, VA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ffcf669df64a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8238eb36278723</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Solution Engineer - Data Engineering Specialist (FSI)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Capp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kinesis, Snowflake, PySpark, Kafka, Hadoop, Python, SQL, R</t>
+          <t>RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35a9b6aca584743</t>
+          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-stack Software Engineer</t>
+          <t>Customer Journey and Experimentation Team - Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Manulife</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, Git, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Git, Snowflake, PySpark, Hadoop, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d34396f850f076e</t>
+          <t>https://www.indeed.com/viewjob?jk=be562f728dd894e8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Scientist 3</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TSP LLC</t>
+          <t>FreshDirect</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Woodbridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data Scientist, Git, Snowflake, Databricks, PySpark, Tableau, Quicksight, Python, SQL, R</t>
+          <t>RAG, Gemini, Prompt Engineering, CI/CD, MySQL, Power BI, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8136792201f6bfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=195a6dceff4f5296</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PropertyPilot</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Manasquan, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Redshift, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dab1f6a4231dbe32</t>
+          <t>https://www.indeed.com/viewjob?jk=fac3dd5dd3fe3bac</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python AI/ML</t>
+          <t>Database Engineer - Professional Archive Search</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kinesis, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c05b83413ef699f8</t>
+          <t>https://www.indeed.com/viewjob?jk=607072382f0dc730</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Python/AWS/Kafka</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, Kinesis, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b1af3e74c0a5456</t>
+          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Enterprise AI Architect</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.9</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Azure ML, Synapse, CI/CD, Git, Databricks, PostgreSQL</t>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a69902c54cdf2463</t>
+          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Scientist, Marketing Analytics</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Tableau, Power BI</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=710a55c7263d5b09</t>
+          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Engineer I, AI</t>
+          <t>Senior Machine Learning Engineer- Credit Karma</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, OpenCV, S3, EC2, Docker, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=868c1db97a70677e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc4e58b3ce9d9047</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Engineer I, AI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, OpenCV, S3, EC2, Docker, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, RAG, S3, Git, Snowflake, Hadoop, MySQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d12156e8fb489dcf</t>
+          <t>https://www.indeed.com/viewjob?jk=e117b7084e46100a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Willingboro, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Data Lake, CI/CD, Git, Snowflake, Databricks, Redshift, NoSQL</t>
+          <t>AI Engineer, Generative AI, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,277 +706,277 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e3afe7a50298373</t>
+          <t>https://www.indeed.com/viewjob?jk=794ce59698eaf273</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Intern</t>
+          <t>Sr. Software Engineer - Professional Archive Search &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, S3, Redshift, Data Lake, CI/CD, GitHub Actions, Git, Redshift</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbd60d97bfacc60</t>
+          <t>https://www.indeed.com/viewjob?jk=3161821c87624864</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineering Intern</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bright Machines</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Databricks, BigQuery, Redshift, Tableau, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961161799c7db2e3</t>
+          <t>https://www.indeed.com/viewjob?jk=9471435ad6b60d22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Nexnovels</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Databricks, BigQuery, Redshift, Tableau, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75efa56b5158387e</t>
+          <t>https://www.indeed.com/viewjob?jk=95a2160d7866d722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Software Engineer - Professional Archive Search</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245c39b07398f5a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7687f72259bef67c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Software Engineer - Ingestion</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1389dbc20ceca1f2</t>
+          <t>https://www.indeed.com/viewjob?jk=b0d3866d1f6e8ab4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Software Engineer - Ingestion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Clemente, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b5d6530b9c6e9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=76ad4a33f5c294e9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Software Engineer - Professional Archive Search</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Smarsh</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Escondido, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b5cd590389fcb8</t>
+          <t>https://www.indeed.com/viewjob?jk=f1561e94ab8471a9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Senior Distinguished Engineer, AI Compute (Remote Eligible)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>AI Engineer, Generative AI, RAG, EC2, Kubernetes, Dask, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23a60a85ba8e33b8</t>
+          <t>https://www.indeed.com/viewjob?jk=f72821a4b032f240</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Corporate- AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04eed1b8662a64c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a32360114ec01c40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Java Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sparks, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=639c879094c2c1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Machine Learning Engineering - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oceanside, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a2de883e7fa22dc</t>
+          <t>https://www.indeed.com/viewjob?jk=042042bfe6828e57</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist, Ai Infrastructure and MCP (onsite)</t>
+          <t>Technical Operations Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Codoxo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, R</t>
+          <t>RAG, S3, Data Lake, NoSQL, Quicksight, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8238eb36278723</t>
+          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capp</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Azure ML, MLflow, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Databricks</t>
+          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,112 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5005229862766ee1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Customer Journey and Experimentation Team - Data Scientist Senior Associate</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Snowflake, PySpark, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=be562f728dd894e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>FreshDirect</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Woodbridge, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Prompt Engineering, CI/CD, MySQL, Power BI, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=195a6dceff4f5296</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Red Hat</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fac3dd5dd3fe3bac</t>
+          <t>https://www.indeed.com/viewjob?jk=a3dc418569d8cd40</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Database Engineer - Professional Archive Search</t>
+          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Morgan Stanley</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,42 +486,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Kafka, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Cortex, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=607072382f0dc730</t>
+          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Full Stack Senior Software Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=458f2e64ebd817f0</t>
+          <t>https://www.indeed.com/viewjob?jk=706807ad34e1847c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>REsurety</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Terraform, Snowflake, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dc21140836b0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c2975c0f289dc27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps with IoT focus</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intellimation LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Git, Kafka, NoSQL, Python, SQL</t>
+          <t>RAG, Gemini, EC2, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,567 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35c20a436a0a3121</t>
+          <t>https://www.indeed.com/viewjob?jk=20dffbddb7c9c7eb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer- Credit Karma</t>
+          <t>Senior Data Engineer (AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>Capnexus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Dataflow, Kubernetes, Databricks, Dask, Python, SQL</t>
+          <t>Generative AI, RAG, S3, Glue, Data Lake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc4e58b3ce9d9047</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Git, Snowflake, Hadoop, MySQL, Tableau, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e117b7084e46100a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=794ce59698eaf273</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Professional Archive Search &amp; AI</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3161821c87624864</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Databricks, BigQuery, Redshift, Tableau, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9471435ad6b60d22</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Databricks, BigQuery, Redshift, Tableau, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95a2160d7866d722</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer - Professional Archive Search</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7687f72259bef67c</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer - Ingestion</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0d3866d1f6e8ab4</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Software Engineer - Ingestion</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76ad4a33f5c294e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Software Engineer - Professional Archive Search</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Smarsh</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f1561e94ab8471a9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Senior Distinguished Engineer, AI Compute (Remote Eligible)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, EC2, Kubernetes, Dask, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f72821a4b032f240</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Corporate- AI Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RHP Properties</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Farmington Hills, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a32360114ec01c40</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Java Software Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93e94130ade15aac</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineering - Intelligent Foundations and Experiences (IFX)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=042042bfe6828e57</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Technical Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Codoxo</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, S3, Data Lake, NoSQL, Quicksight, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e78a417a0f4410ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Orion180 Insurance Services, LLC</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3dc418569d8cd40</t>
+          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE) - AI Platform &amp; Cloud</t>
+          <t>AI Engineer - Insurance Domain - HYBRID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Morgan Stanley</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Docker, Kubernetes, Terraform, Git, Snowflake, Kafka, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Pinecone, ChromaDB, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67434a699408c40f</t>
+          <t>https://www.indeed.com/viewjob?jk=aeda85e53ae1234a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Developer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=706807ad34e1847c</t>
+          <t>https://www.indeed.com/viewjob?jk=5860326bcd41826a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Science Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>REsurety</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>23.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Terraform, Snowflake, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c2975c0f289dc27</t>
+          <t>https://www.indeed.com/viewjob?jk=7c7ee3a099eaf443</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps with IoT focus</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intellimation LLC</t>
+          <t>Q2ebanking</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Gemini, EC2, Terraform, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, AWS SageMaker, Glue, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20dffbddb7c9c7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc44924f0b95abaf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS)</t>
+          <t>Senior Analytics Engineer (Platform - Financial Analytics)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capnexus</t>
+          <t>Coinbase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,21 +622,6706 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Copilot, Prompt Engineering, Data Lake, Kinesis, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81cb8276b9830117</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1025fbeafa9ab455</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Scientist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Metropolitan Commercial Bank</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91dc407cffdf4464</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer, ARIA Team</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Mistral, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cc8ca02d0956110</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Kinesis, FastAPI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3dc51ebaa811edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Kinesis, FastAPI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3b52af53d359ea1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Cross River Bank</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fort Lee, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Data Lake, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b50d648e96c1629</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>eClinical Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, S3, EC2, MLflow, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc6ebe88367f5090</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Database Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NetDocuments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Glue, Kinesis, CI/CD, Terraform, Snowflake, Kafka, PostgreSQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31b06bf0600541ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Focus Financial Partners</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Git, Snowflake</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc6ec804cfff5642</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer - React and Python/Node</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Codal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BigQuery, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, BigQuery</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fc9aafe56da8514</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Backend Engineer II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>HackerRank Careers</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, CI/CD, Git, Kafka, PostgreSQL, MySQL, NoSQL</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4979e4cfe40ed8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI-ML Engineer 1</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Universal Avionics Systems Corporation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tucson, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Keras, S3, EC2, Docker, Kubernetes, Git, Hadoop</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3e0f3955fde63ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Engineer | The Points Guy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec2d5686f500c7c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer | The Points Guy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, BigQuery</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac5793781d1c8a3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer | The Points Guy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Data Lake, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa160af377aea6a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 3, Resi</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Pushpay</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Allen, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, Gemini, Copilot, Docker, Kubernetes, CI/CD, Jenkins, Git, MySQL, Cassandra</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46720efbc4179e48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=564c2131c7a47b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Engineer (Gen AI)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Interactive Brokers</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Glue, Athena, Data Lake, Docker, CI/CD, Git, PySpark</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5cd87f5af20caa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Full- Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Monks</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9829e6750566d9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Remote, US)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Kubernetes, CI/CD, Terraform, Git, BigQuery, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c31bc8d5bad8edcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Frederick, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=353f08220bc3960e</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>JENSEN HUGHES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, XGBoost, MLflow, Git, Databricks, PySpark, Power BI, Matplotlib, Python</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4e1a90130e82ea2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Computer Programmer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3f8d985ccebf8fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Pulse</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b16488e544d680f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Pulse</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, S3, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MySQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84b1250e6d4884f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OpenAM</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Git, Kafka</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=587c91d4f597e019</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist I</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>GumGum</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Santa Monica, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, PyTorch, OpenCV, Snowflake, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5eb3c27975ee433</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Point Digital Finance</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Cortex, S3, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e982505dce1ac7b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sr Field Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Striim</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, Git, Snowflake, Databricks, BigQuery, Kafka, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23cfb9e733715fe0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (full-stack)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ithaka</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04dea39109a84481</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1313e128688f3693</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, S3, Docker, Kubernetes, CI/CD, Git, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5882b43322568ab3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Junior Software Engineer – Scientific Computing (C++)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Copilot, Mistral, Hugging Face, Prompt Engineering, Docker, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9bb6e66f86e2b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gametime United</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24a25e68a1bd6d4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Authenticx</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, spaCy, Docker, Kubernetes, Matplotlib, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04a6915b9256fa30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Recommendations (Experience)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Soundcloud</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=825e33ce337f43b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Keras, Kubernetes, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c80a1d5bbc760f6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Synapse, Apache Airflow, Git, Snowflake, Databricks, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ab0f8e743dbbc8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Health-E Commerce</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Synapse, Apache Airflow, Git, Snowflake, Databricks, BigQuery, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b75ba4eaa7e2f72</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd98e6c90182dad1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1188cf2ae8e587af</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Metropolis</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, PostgreSQL, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec0dc8f9f8c8d698</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TripleLift</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Git, Snowflake, Databricks, MySQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=966732011a62a052</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Commercial Loans Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f330b266e75eb445</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Advisory Architect, Data/AI Due Diligence- TTS</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Glue, Data Lake, Kinesis, Snowflake, Databricks, Kafka, NoSQL, Tableau, Quicksight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5239f6ce7d60780b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PingOne Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Data Lake, MLflow, CI/CD, Terraform, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7da86ff81783692d</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tenable</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Columbia, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a30cfbf696f3ce41</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Engineer, Developer Platform (Cloud Apps)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, S3, EC2, CI/CD, Jenkins, Terraform, Git, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a10c8d4659b2bc91</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Mid-Level Data Scientist</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USAA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5d4218922358e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Interwell Health</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Prompt Engineering, Data Lake, AKS, CI/CD, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c820c758b7322ab4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Senior Database Administrator</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NetDocuments</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Kinesis, Kubernetes, Terraform, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d416fca036fe4ced</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AI Data Scientist</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Hunter Douglas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Copilot, Git, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c24c6d47af7af61f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Data and Analytics Consultant</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Data Lake, Snowflake, Databricks, Redshift, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7673e6d45c8d4492</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b91c9070c3ca5e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Headspace</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Data Lake, Terraform, Snowflake, Databricks, Redshift, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbb7191dcfe18f53</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Applied Scientist II</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Coalition Inc.</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, XGBoost, LightGBM, MLflow, Git, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e3e9b4f3ac9a56c</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>OneStudyTeam</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Athena, Docker, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=156a4c762a06a207</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=938e3a94076bba8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hugging Face, TensorFlow, PyTorch, Keras, spaCy, NLTK, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d288cb2e4b349f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Architect- Enterprise Systems</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Toshiba Global Commerce Solutions</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1c0ff375c28735e</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Software Development Engineer 1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>ISPOT</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=344da077a57b830d</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Learning Commons</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a306e1772cf68451</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>WA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e6a0ff1e37821ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Git, Kafka, Hadoop, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e149a4482a17c3cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cross River Bank</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Fort Lee, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=988102e17b80f0cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Solutions Engineer(Python/Airflow)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EDB</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c8018d5fd5cf770</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ivanti</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, AKS, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61e37477d66c760d</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - AI Product</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Re:Build Manufacturing</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0402ee6f14d2048</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer - AI Product</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Re:Build Manufacturing</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FastAPI, Docker, CI/CD, Terraform, PostgreSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c8eae46b7e8c415</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Growth</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Terraform, Git, MySQL, Cassandra, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47005ee78426fbaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Contributory Network</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Waltham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Dataflow, Kubernetes, Apache Airflow, Terraform, Snowflake, BigQuery, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a1c158c64508404</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Known</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, Terraform, Git, Snowflake, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a085730dfa7f8356</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior AI Product Engineer | Growth and Transformation</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Red Ventures</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, CI/CD, GitHub Actions, Terraform, Git, Kafka, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=010e21e577894ff9</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Platform/DevOps Engineer (Kubernetes-Linux)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e75674dc09b32a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer/ Architecture (ADF &amp; Databricks)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>United Vein &amp; Vascular Centers</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=443e4c4dac7242b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Fairstead</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01d86f7198f3a7a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Administrator - Austin, TX ONLY</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Industrial Electric Manufacturing</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f880ca8069252710</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d720423e315faa8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior MuleSoft Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Green Irony</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe418f28e59352b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Snowflake, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72ccbb4273f0fe52</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Solutions Architect - AI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Glue, Redshift, CI/CD, Terraform, Redshift, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f834b4ee8d5a00bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Kinesis, Snowflake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37438e3b4025f8ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Scientist - Healthcare Supply Chain Riskdata</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Exiger</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e06b5de82f1acf0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, AI/ML</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Icon</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Prompt Engineering, PyTorch, FastAPI, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ab75a53c0dedd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5b43c88565030fc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c738eb29aa58357</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Tebra</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Data Lake, CI/CD, Snowflake, Databricks, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ff32c43e9fb05be</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Data Platform</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Data Lake, Kafka, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d11d564008211662</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Apache Airflow, CI/CD, Terraform, Git, Databricks, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e3a17b22e5142267</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer, Data Mining</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Motional</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, AKS, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4df8f932301b2532</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Control Plane</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Aerospike</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1c92cd50ce96c5bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d84672da0876f639</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Hadoop, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef4107f2b97f4abb</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Data Scientist - Production Engineering</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Cordial</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Data Scientist, S3, Glue, Athena, BigQuery, Snowflake, BigQuery, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=118eeac9c372738d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Applied AI Analyst</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Metropolitan Commercial Bank</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a223b45d3362c204</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>C4ADS</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f772a6fcda1f62ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Consultant - AI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3Cloud</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Copilot, FAISS, Pinecone, Git, Databricks, Power BI, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2a5dc67cb94e5bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Git, PySpark, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8938c74cf419f4dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Pager Health</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3542577aa4c2c9d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Full-Stack, Revenue Growth</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Paperless Post</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Kubernetes, Terraform, PostgreSQL, MongoDB, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3f53f730f59a2c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Devsecops Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Fustis LLC</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d599393e6cdc0579</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Forward-Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d885b614b5760cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Forward-Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Cohere Health</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>S3, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68d501293b90ee95</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Buyers Edge Platform</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c82c1ce7f2620a4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Revenue Systems Architect</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Instawork</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Redshift, Git, Snowflake, Redshift, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f783ed05316cf0ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SecurityScorecard</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=817ee8763e326e07</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SecurityScorecard</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43aadc34d71af986</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SecurityScorecard</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb1f08094947da90</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, OpenCV, Kubernetes, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8127099d559be0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, Keras, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc87b5916fbf015d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Medeloop</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3187da15325fa95f</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer – Backend</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CaseGuard</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>S3, EC2, Docker, Kubernetes, Terraform, NoSQL, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7a969f5c65d3bc93</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Sr. Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Fairlife, LLC</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f203c334e20f61e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Robotics</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, OpenCV, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d3e005fb5f130ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior Quality Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Circle.so</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3752971091aeeac9</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Fellow</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a85ca73728251e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Synapse Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b8776f8a892c21e</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f57661e258e72a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer-Public Cloud</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ensono</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa6f15eda406edac</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer, Video Input/Output Systems</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Fubo</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Python, SQL, R, Java, Scala, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=027edfb89c34d83b</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Research Engineer, FlexOlmo</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>The Allen Institute for Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, spaCy, Docker, AKS, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6b192f58e21976f</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Computer Vision &amp; ML, Cross-Domain AI</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Lanham, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, MLflow, CI/CD, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d285cdc73f7ee07</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bold</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Guaynabo, PR, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d54f38eb2c7285cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer | Cloud</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>ExtraHop Networks</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=13432b736773845c</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Wayve</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, PyTorch, Hadoop, Python, SQL, R, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40ba6603057e479d</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior C++ Software Engineer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DIVERGENT</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>RAG, OpenCV, CI/CD, GitHub Actions, Git, Python, R, C++, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e137f22e48a85900</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, AI Security Platform</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b345e5bcc1dc2479</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, AI Security Platform</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BeyondTrust</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bca5e4408aa07478</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Back End Engineer [Remote-US]</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Quanata</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, R</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c1cb8fc0d6db275</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, XGBoost, AWS SageMaker, MLflow, Docker, CI/CD, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45a4066409f12d50</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, XGBoost, AWS SageMaker, MLflow, Docker, CI/CD, PySpark, Python, R</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfe11c5ceb3fb6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=12a60647eba4ace7</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fd8203405f742de</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Senior AI/ML Engineer, Production AI (Contractor)</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Legend Biotech</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Somerset, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c844df5e0b9139bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Sr. Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Cordial</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=23796f6dc0a5fe83</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>MacroHealth</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d2770cefb52d3a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>MacroHealth</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Kirkland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b13328aa6e451ea6</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Digital Health And Behavior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Axle</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=565c065b96815595</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior AI Scientist – Transportation &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Avathon</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Kafka, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46f48f669c75fa58</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e5aa7f7d7f8e2576</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60ce0e464be543cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Software Developer II - Customer Care &amp; Billing Utility Software (Front End)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>National Information Solutions Cooperative (NISC)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, Git, Kafka, Cassandra, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=012e65aeefbde288</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Senior Consultant | AI Strategy (Remote)</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Trace3</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d01fd7a54a3a217</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Automation Engineer (Mid level SDET)</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Medrio</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d8b1483af03cf54</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pansophic Learning</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Tysons, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>S3, EC2, Redshift, Git, Redshift, MongoDB, NoSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67a44bf81f0910e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Netsmart Technologies</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, S3, Glue, Data Lake, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7b11ddd229f030</t>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17857985583e28da</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>RZR Global Inc.</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f23e2158af0b7551</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>AI Tutor - Crypto</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Xai</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, TensorFlow, PyTorch, Git, Polars, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ab95330f8243d35</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, NLP</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Datavant</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Databricks, PySpark, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed1d638a833823bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sr. Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Mochi Health</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d1a85184037bd1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Front-End Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Mochi Health</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b983bf44997c7d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Industrial Electric Manufacturing</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>10</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Copilot, CI/CD, Git, Snowflake, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8dcfe7e6a54378e</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Endpoint Engineer</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9adeefd04c84744a</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Sr. Python Engineer (Only W2) Locals</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Raag Solutions</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>10</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>PostgreSQL, MySQL, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=940d9f8859f1faf3</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SkillBridge - DevSecOps Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>The Weather Company</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>10</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f5e1509c6a7bf8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>KIZEN Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>10</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Kafka, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=601baad39d101b8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer, Graph Databases</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Hone health</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>10</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=59f389941a8cc84f</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>10</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Kafka, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f2f208946756965</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>10</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Kafka, Hadoop, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ae3aa6e6f6ff303</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Afresh</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>10</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45cb61d7cbc392c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Afresh</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>10</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d666486b9e3f5cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, CI/CD, Snowflake, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a265479586368043</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>FanDuel</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb9acfcb385fd29f</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Computer Vision</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CLEAR</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=910ac47abaaaeb09</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Software Engineer – AI &amp; ML Infrastructure</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Path Robotics, Inc.</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, PyTorch, Docker, AKS, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=347fc898734391ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Cross-Domain AI</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>AST SpaceMobile</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Lanham, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, CI/CD, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a06646b05d66822</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Backend - Platform (Overseer)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Docker, AKS, Kafka, MongoDB, R</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed57d4337c79a7d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I, Client Connections</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EnergyHub</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=30a1bd1ba5ab2ff4</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer III – Computer Vision &amp; Data Systems</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Zone 5 Technologies</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, PyTorch, OpenCV, YOLO, MLflow, CI/CD, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d04d5517f3942adb</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Senior ML Data Engineer (P508)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Data Lake, Dataflow, BigQuery, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9f832d9d7ce36c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SDET [Remote-US]</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Quanata</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9ce749c3d74c6ca0</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=216fe02bd8709eaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Data Science Analyst</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Further</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Snowflake, BigQuery, Python, SQL, R, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5dc5d32e422625d</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Granum</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Cortex, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e0b0fdfba93be5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist, Borrow</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a18315df833a0814</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist Consultant - Agentic Platform (P4339)</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, Prompt Engineering, MLflow, Databricks, PySpark, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d561def3a23fa3e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Full-Stack Engineer, AI Financial Actions &amp; Recommendations</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, PostgreSQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4357771b59754b6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Major League Baseball</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Generative AI, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf5e9f3e3a480930</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SambaNova Systems</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Dataflow, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5be3e42f56dc6e5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Senior Go Software Engineer</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Array</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, MongoDB, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e75357694b70f4de</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Technical Recruiter</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Sigma Computing</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>BigQuery, AKS, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=580e482cb11d86b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, Search Discovery</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Cribl</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RAG, S3, Data Lake, CI/CD, Jenkins, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcb25c80b9c9950a</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Solutions Engineer, SELECT by DoiT</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>DoiT</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, BigQuery, Snowflake, Databricks, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87ae9ba75dc4e2cd</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Senior Perception Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Apptronik</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, YOLO, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=efd51ce7cf941345</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Senior Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Tekmetric</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0168e89a776b4f9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Data Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SimilarWeb</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>RAG, S3, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e039b4fcb467133</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>GTM Engineer</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>InvoiceCloud</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>10</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, Git, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d5a6fb24e3c10486</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Customer Centric Engineer</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Workato</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>10</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>RAG, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2bd2922dc33f7ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>AI Red Teamer</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>HiddenLayer</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>10</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, LLaMA, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=74b59ba90f42ab31</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>10</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ff779f0dce63ada3</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>10</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, Git, Kafka, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9eb55e9f7a6dc231</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-04-22.xlsx
+++ b/daily_matches/job_matches_2026-04-22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Redhorse Corporation</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Docker, Kubernetes, Apache Airflow, CI/CD, Snowflake, BigQuery, Redshift</t>
+          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2430929f4b97ab4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b36e588b24926dd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Engineering</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>U.S. Venture, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Green Bay, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, Redshift, BigQuery, Kinesis, MLflow, Snowflake, Databricks, BigQuery</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, TensorFlow, BigQuery, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2169de43fedb76d3</t>
+          <t>https://www.indeed.com/viewjob?jk=29812a94e195b5ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer &amp; AI Prompt Engineer (GenAI Full Stack)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pacific Health Group</t>
+          <t>Ascendion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, FastAPI</t>
+          <t>S3, Glue, Redshift, Terraform, Git, Snowflake, Databricks, Redshift, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2fe51fda5bf8f2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ede735cbdf2b63e0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Remote US</t>
+          <t>Senior Full-Stack Python Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>N-iX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,46 +587,46 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, Python</t>
+          <t>AI Engineer, RAG, Gemini, FastAPI, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0faea77dd1e82a</t>
+          <t>https://www.indeed.com/viewjob?jk=365bb0b9ec3ce321</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Entry-Level AI Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C2 Technologies Inc</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Prompt Engineering, TensorFlow, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Snowflake, Redshift, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baf3a33721556697</t>
+          <t>https://www.indeed.com/viewjob?jk=4a6e4d5ab8b9b5fa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>NLP LLM Specialist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Wisconsin–Madison</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, AKS, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, NLP Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, spaCy, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ad5e385a9b79a74</t>
+          <t>https://www.indeed.com/viewjob?jk=9b16170aae29e935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer | Digital Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Beta Technologies</t>
+          <t>DOW</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>Midland, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,64 +696,64 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Data Lake, Kinesis, Docker, Kubernetes, CI/CD, Git, Kafka, Python</t>
+          <t>RAG, CI/CD, Terraform, Git, Snowflake, Databricks, PySpark, Tableau, Power BI, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf9a4a981492f65f</t>
+          <t>https://www.indeed.com/viewjob?jk=0e6f52d2577111f6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (Data Modeling &amp; BI)</t>
+          <t>AI/ML Research Engineer, LLM Post-Training &amp; Evaluation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, Git, Snowflake, Redshift, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b319560288703a69</t>
+          <t>https://www.indeed.com/viewjob?jk=0032995c2cb8dacf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer, Analytics &amp; Machine Learning Enablement</t>
+          <t>AI/ML Research Engineer, LLM Post-Training &amp; Evaluation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,73 +762,73 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, Glue, Redshift, BigQuery, CI/CD, Git, Snowflake, BigQuery, Redshift, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, CI/CD, Python, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b569d0296983d6a1</t>
+          <t>https://www.indeed.com/viewjob?jk=734f46ed5ad16889</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mid-Junior DevOps Engineer - USA</t>
+          <t>Sr. Platform Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HERE Technologies</t>
+          <t>archer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c2461cde24df9</t>
+          <t>https://www.indeed.com/viewjob?jk=e910893e7900f872</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Product</t>
+          <t>Site Reliability Automation Engineer (contract)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ware Malcomb</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d944819ec0623121</t>
+          <t>https://www.indeed.com/viewjob?jk=65696ea7b7ab0b81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jr DevOps Engineer</t>
+          <t>Data Scientist - Applied Science</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Patrick J. McGovern Foundation</t>
+          <t>Future Secure AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, spaCy, NLTK, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=360a895e2e384db3</t>
+          <t>https://www.indeed.com/viewjob?jk=be84836031856fec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software &amp; AI Engineer III</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b125c18c2755f2</t>
+          <t>https://www.indeed.com/viewjob?jk=16179533179bf6b7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist/ HR</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Laurate LLC</t>
+          <t>Integral Ad Science</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Renton, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c929b507a68fea2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f3a5eee6b5267d17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior CAD Backend Engineer - Mechanical/CAD Automation (CAD API Expertise)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38003ef92702fb2c</t>
+          <t>https://www.indeed.com/viewjob?jk=aab1151c5a1ee22d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior CAD Backend Engineer - Mechanical/CAD Automation (CAD API Expertise)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=249c20f607feb602</t>
+          <t>https://www.indeed.com/viewjob?jk=65848bce107d0e66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Business Systems Automation Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CentralReach</t>
+          <t>RVO Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Holmdel, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Git, Tableau, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed48554936f90cc</t>
+          <t>https://www.indeed.com/viewjob?jk=e38371faba972b31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer, Platform &amp; Infrastructure</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Verse</t>
+          <t>KNOTCH, INC.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Git, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,164 +1091,164 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e500b50c02893324</t>
+          <t>https://www.indeed.com/viewjob?jk=16ae92b0f1285c93</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI/ML Specialist Solution Architect (Early Talent)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Kafka, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>Hugging Face, TensorFlow, PyTorch, Docker, Kubernetes, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d5ed5812f358811</t>
+          <t>https://www.indeed.com/viewjob?jk=5e73f7685c3973e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>SQL/ETL Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>Stream Companies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>TensorFlow, PyTorch, Keras, spaCy, NLTK, OpenCV, S3, Python, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c059e9218f7e23d</t>
+          <t>https://www.indeed.com/viewjob?jk=11a6d536551ee780</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Graduate ML Engineering Intern</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RapidSOS</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, Python, R, Scala</t>
+          <t>RAG, LLaMA, TensorFlow, PyTorch, Azure ML, MLflow, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3986c9d7e69f169</t>
+          <t>https://www.indeed.com/viewjob?jk=98841c207b25b87d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Cybersecurity / Threat Detection</t>
+          <t>Sr. Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Streamline Healthcare Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Gemini, Hugging Face, Prompt Engineering, Docker, Git, Python, R, Scala, Optimization</t>
+          <t>Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c84f25cc8bd9e6</t>
+          <t>https://www.indeed.com/viewjob?jk=20ae2aaa86ff3339</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist - Atlanta, GA</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cortland</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1a1396b0ef192c</t>
+          <t>https://www.indeed.com/viewjob?jk=abe13c997a0c0d13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer II</t>
+          <t>Senior Backend Engineer, Workflow Systems</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Smarsh</t>
+          <t>Kinstead</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,77 +1301,742 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f29b35bf06d63d30</t>
+          <t>https://www.indeed.com/viewjob?jk=d5852043f61b0be3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Database Integrations (Go/React)</t>
+          <t>Senior Product Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>Kinstead</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, GitHub Actions, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ddbb9189a1341</t>
+          <t>https://www.indeed.com/viewjob?jk=e7d25416626ea325</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Technical Advisor, Intellectual Property</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CARVANA</t>
+          <t>DataRobot</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, CI/CD, Terraform, Git, MongoDB, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f762afb66c18f39</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Quality Engineer - Performance</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OneTrust</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Jenkins, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3828db95a644b84f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>COVU Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, S3, Git, Snowflake, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06a241e7c595256d</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Microsoft Ai &amp; Automation Engineer – Productivity Intelligence (Financial Services)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24e5331786956938</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Microsoft Ai &amp; Automation Engineer – Productivity Intelligence (Financial Services)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=542c3e070f1430ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Java Full Stack Developer (contract)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Docker, AKS, CI/CD, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f6f5017fe9fe2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist, Applied Science</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Future Secure AI</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Git, Python, R, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66d2839aea5a962a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Future Secure AI</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1782191d6b3ed3c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Backend)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nebius</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, PostgreSQL, MongoDB, NoSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8683fed71b4559a</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ResultStack</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, Docker, CI/CD, Git, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=869550fa08d2fe12</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BridgeNexus Technologies Inc</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=93aa9cda95c2f71d</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fca965bcc2f5d701</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Analytics (Backend)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OneSignal</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Kafka, PostgreSQL, Cassandra, NoSQL, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b778d18b36fc17ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Fullstack Engineer - Observability Real User Monitoring (RUM) | US | Remote</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Grafana Labs</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Docker, Kubernetes, Kafka, Cassandra, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44257fd541305ac2</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Developer-First &amp; Tools Software Engineer, AISW Group</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, CI/CD, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aa6e3a377577a59</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Cellebrite</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AI Engineer, PyTorch, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f09d50a533880ea1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI Software Engineer - HP IQ</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, NoSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67be784eb2fe8052</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Warranty Data Analyst / Data Scientist</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2ffd491a76c9fa66</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Data Sciences</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Madison, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7b080ce6c869dde</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>University of Maryland Medical System</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>North Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, Hadoop, PostgreSQL, MongoDB, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4188adfee24d1373</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Senior Specialist - Architecture</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LTIMindtree</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Java, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e70c4d98f2e17ef5</t>
         </is>
       </c>
     </row>
